--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chens\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wyh/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02504AF-84CA-4470-8937-A3217922EB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAD15A9-DDB6-8747-8804-1243DB47D466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -165,12 +165,24 @@
   <si>
     <t>Let the user choose the data-generating distribution</t>
   </si>
+  <si>
+    <t>Yaohe Wang</t>
+  </si>
+  <si>
+    <t>wang3548</t>
+  </si>
+  <si>
+    <t>q1ngyao</t>
+  </si>
+  <si>
+    <t>https://github.com/q1ngyao</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -220,6 +232,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -244,10 +264,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -261,8 +282,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -480,17 +503,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" customWidth="1"/>
+    <col min="1" max="1" width="31.5" customWidth="1"/>
     <col min="2" max="2" width="76" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -498,7 +521,7 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -506,7 +529,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -514,7 +537,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -522,7 +545,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -530,7 +553,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -538,17 +561,17 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
       <c r="B8" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
       <c r="B9" s="7"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
@@ -556,7 +579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
@@ -564,7 +587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
@@ -572,31 +595,31 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1"/>
       <c r="B20" s="3" t="s">
         <v>8</v>
@@ -614,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
@@ -630,53 +653,72 @@
       <c r="E21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22">
+        <v>1008795074</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F22" r:id="rId1" xr:uid="{D584214A-2DB4-8340-A7D5-9C0FAE353B4C}"/>
+    <hyperlink ref="F21" r:id="rId2" xr:uid="{BC2B251F-8CB0-9A45-AB30-6F4E627C4619}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wyh/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAD15A9-DDB6-8747-8804-1243DB47D466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="21960" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -41,89 +35,36 @@
     <t>Group Name:</t>
   </si>
   <si>
+    <t>GG Bond</t>
+  </si>
+  <si>
     <t>Desired Topics:</t>
   </si>
   <si>
     <t>Topic Number 1</t>
   </si>
   <si>
+    <t>Random Variable Generation</t>
+  </si>
+  <si>
     <t>Simulated distributions, if applicable:</t>
   </si>
   <si>
+    <t>Acceptance-Rejection (choose 2):</t>
+  </si>
+  <si>
     <t>Extra details:</t>
   </si>
   <si>
-    <t>Topic Number 2</t>
-  </si>
-  <si>
-    <t>Topic Number 3</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>UtorID</t>
-  </si>
-  <si>
-    <t>Student Number</t>
-  </si>
-  <si>
-    <t>GitHub Username</t>
-  </si>
-  <si>
-    <t>GitHub URL</t>
-  </si>
-  <si>
-    <t>Student 1</t>
-  </si>
-  <si>
-    <t>Student 2</t>
-  </si>
-  <si>
-    <t>Student 3</t>
-  </si>
-  <si>
-    <t>Student 4</t>
-  </si>
-  <si>
-    <t>Student 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each group member is expected to contribute equally to the project. It is the responsibility of the group to allocate duties fairly, understanding that not everyone needs to be involved in every task. </t>
-  </si>
-  <si>
-    <t>For instance, it may not be feasible for all members to meet and collect data together.</t>
-  </si>
-  <si>
-    <t>All students within the same group will receive the same mark. However, your grade may be reduced if most of your group reports that you did not contribute or cooperate adequately.</t>
-  </si>
-  <si>
-    <t>To report an inactive member, please refer to the "Reporting Inactive Members" section under the project description.</t>
-  </si>
-  <si>
-    <t>Shijun Chen</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>chens531</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CSJ111</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://github.com/CSJ111</t>
-  </si>
-  <si>
-    <t>GG Bond</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Random Variable Generation</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Beta(α, β)</t>
     </r>
     <r>
@@ -131,7 +72,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (very relevant: Bernoulli probability modeling, bandits)</t>
@@ -139,6 +80,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Gamma(k, θ)</t>
     </r>
     <r>
@@ -146,15 +95,14 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (common in Bayesian models; waiting times)</t>
     </r>
   </si>
   <si>
-    <t>Acceptance-Rejection (choose 2):</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>Topic Number 2</t>
   </si>
   <si>
     <t>Monte Carlo Simulation of a Hypothesis Test</t>
@@ -166,6 +114,42 @@
     <t>Let the user choose the data-generating distribution</t>
   </si>
   <si>
+    <t>Topic Number 3</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>UtorID</t>
+  </si>
+  <si>
+    <t>Student Number</t>
+  </si>
+  <si>
+    <t>GitHub Username</t>
+  </si>
+  <si>
+    <t>GitHub URL</t>
+  </si>
+  <si>
+    <t>Student 1</t>
+  </si>
+  <si>
+    <t>Shijun Chen</t>
+  </si>
+  <si>
+    <t>chens531</t>
+  </si>
+  <si>
+    <t>CSJ111</t>
+  </si>
+  <si>
+    <t>https://github.com/CSJ111</t>
+  </si>
+  <si>
+    <t>Student 2</t>
+  </si>
+  <si>
     <t>Yaohe Wang</t>
   </si>
   <si>
@@ -176,23 +160,64 @@
   </si>
   <si>
     <t>https://github.com/q1ngyao</t>
+  </si>
+  <si>
+    <t>Student 3</t>
+  </si>
+  <si>
+    <t>Meizhi Dong</t>
+  </si>
+  <si>
+    <t>dongmeiz</t>
+  </si>
+  <si>
+    <t>DMZ66</t>
+  </si>
+  <si>
+    <t>https://github.com/DMZ66</t>
+  </si>
+  <si>
+    <t>Student 4</t>
+  </si>
+  <si>
+    <t>Student 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each group member is expected to contribute equally to the project. It is the responsibility of the group to allocate duties fairly, understanding that not everyone needs to be involved in every task. </t>
+  </si>
+  <si>
+    <t>For instance, it may not be feasible for all members to meet and collect data together.</t>
+  </si>
+  <si>
+    <t>All students within the same group will receive the same mark. However, your grade may be reduced if most of your group reports that you did not contribute or cooperate adequately.</t>
+  </si>
+  <si>
+    <t>To report an inactive member, please refer to the "Reporting Inactive Members" section under the project description.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -201,6 +226,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -208,12 +234,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -221,7 +241,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -229,7 +249,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -237,11 +257,154 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,8 +417,194 @@
         <bgColor rgb="FFC9DAF8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -263,39 +612,321 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -493,27 +1124,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
-    <col min="2" max="2" width="76" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
+    <col min="3" max="3" width="15.3303571428571" customWidth="1"/>
+    <col min="4" max="4" width="18.1607142857143" customWidth="1"/>
     <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.3303571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" customHeight="1" spans="1:4">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -521,204 +1151,219 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" customHeight="1" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" customHeight="1" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:2">
       <c r="A8" s="3"/>
-      <c r="B8" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:2">
       <c r="A9" s="3"/>
       <c r="B9" s="7"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" customHeight="1" spans="1:2">
       <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:2">
+      <c r="A11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:1">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" customHeight="1" spans="1:1">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" customHeight="1" spans="1:1">
       <c r="A15" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:1">
       <c r="A16" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:1">
       <c r="A17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:1">
       <c r="A18" s="3"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="1"/>
       <c r="B20" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D21">
         <v>1009305716</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" customHeight="1" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="D22">
         <v>1008795074</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:6">
+      <c r="A23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23">
+        <v>1007241307</v>
+      </c>
+      <c r="E23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:1">
+      <c r="A24" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="9" t="s">
+    </row>
+    <row r="25" customHeight="1" spans="1:1">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="4" t="s">
-        <v>21</v>
+    <row r="27" customHeight="1" spans="1:1">
+      <c r="A27" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:1">
+      <c r="A28" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:1">
+      <c r="A29" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:1">
+      <c r="A30" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F22" r:id="rId1" xr:uid="{D584214A-2DB4-8340-A7D5-9C0FAE353B4C}"/>
-    <hyperlink ref="F21" r:id="rId2" xr:uid="{BC2B251F-8CB0-9A45-AB30-6F4E627C4619}"/>
+    <hyperlink ref="F22" r:id="rId1" display="https://github.com/q1ngyao"/>
+    <hyperlink ref="F21" r:id="rId2" display="https://github.com/CSJ111"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView windowWidth="21960" windowHeight="12680"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -28,104 +44,79 @@
     <t>Topic Number 1</t>
   </si>
   <si>
-    <t>Random Variable Generation</t>
+    <t>Monte Carlo Simulation of a Hypothesis Test(Topic 5)</t>
   </si>
   <si>
     <t>Simulated distributions, if applicable:</t>
   </si>
   <si>
-    <t>Acceptance-Rejection (choose 2):</t>
+    <t xml:space="preserve">Laplace Distribution  </t>
   </si>
   <si>
     <t>Extra details:</t>
+  </si>
+  <si>
+    <t>We use Monte Carlo simulation to study the Type I error and power of the one-sample t-test when data are generated from a Laplace distribution, illustrating finite-sample deviations from normal-theory assumptions.</t>
+  </si>
+  <si>
+    <t>Topic Number 2</t>
+  </si>
+  <si>
+    <t>Acceptance-Rejection Method(Topic 2)</t>
+  </si>
+  <si>
+    <t>Acceptance-Rejection for Laplace Distribution</t>
+  </si>
+  <si>
+    <t>We use the acceptance–rejection method to generate random samples from the Laplace distribution and assess the accuracy of the simulated results by comparing the empirical density, mean, and variance with their theoretical counterparts.</t>
+  </si>
+  <si>
+    <t>Topic Number 3</t>
+  </si>
+  <si>
+    <t>Monte Carlo Analysis of Estimator Performance(Topic 7)</t>
+  </si>
+  <si>
+    <t>Logistic Distribution</t>
+  </si>
+  <si>
+    <t>We use Monte Carlo simulation to compare the performance of the sample mean and sample median as estimators of the location parameter under a logistic distribution, using Pitman closeness as the primary evaluation criterion.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>UtorID</t>
+  </si>
+  <si>
+    <t>Student Number</t>
+  </si>
+  <si>
+    <t>GitHub Username</t>
+  </si>
+  <si>
+    <t>GitHub URL</t>
+  </si>
+  <si>
+    <t>Student 1</t>
+  </si>
+  <si>
+    <t>Shijun Chen</t>
+  </si>
+  <si>
+    <t>chens531</t>
+  </si>
+  <si>
+    <t>CSJ111</t>
   </si>
   <si>
     <r>
       <rPr>
-        <b val="1"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Beta(α, β)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> (very relevant: Bernoulli probability modeling, bandits)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="1"/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Gamma(k, θ)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> (common in Bayesian models; waiting times)</t>
-    </r>
-  </si>
-  <si>
-    <t>Topic Number 2</t>
-  </si>
-  <si>
-    <t>Monte Carlo Simulation of a Hypothesis Test</t>
-  </si>
-  <si>
-    <t>Use distributions that highlight why robust losses exist.</t>
-  </si>
-  <si>
-    <t>Let the user choose the data-generating distribution</t>
-  </si>
-  <si>
-    <t>Topic Number 3</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>UtorID</t>
-  </si>
-  <si>
-    <t>Student Number</t>
-  </si>
-  <si>
-    <t>GitHub Username</t>
-  </si>
-  <si>
-    <t>GitHub URL</t>
-  </si>
-  <si>
-    <t>Student 1</t>
-  </si>
-  <si>
-    <t>Shijun Chen</t>
-  </si>
-  <si>
-    <t>chens531</t>
-  </si>
-  <si>
-    <t>CSJ111</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="12"/>
         <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>https://github.com/CSJ111</t>
     </r>
@@ -145,10 +136,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="12"/>
         <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>https://github.com/q1ngyao</t>
     </r>
@@ -183,10 +175,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="12"/>
         <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>https://github.com/char1029</t>
     </r>
@@ -210,47 +203,201 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="1"/>
+      <b/>
+      <i/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -260,17 +407,203 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="11"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -296,34 +629,6 @@
         <color indexed="10"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -385,9 +690,30 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -399,122 +725,420 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffc9daf8"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ff1155cc"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00C9DAF8"/>
+      <rgbColor rgb="00AAAAAA"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="001155CC"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -713,8 +1337,6 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
@@ -734,19 +1356,19 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Arial"/>
-            <a:ea typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-            <a:sym typeface="Arial"/>
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Arial" panose="020B0604020202090204"/>
+            <a:ea typeface="Arial" panose="020B0604020202090204"/>
+            <a:cs typeface="Arial" panose="020B0604020202090204"/>
+            <a:sym typeface="Arial" panose="020B0604020202090204"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -763,7 +1385,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -788,7 +1410,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -813,7 +1435,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -838,7 +1460,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -863,7 +1485,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -888,7 +1510,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -913,7 +1535,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -938,7 +1560,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -963,7 +1585,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -976,9 +1598,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -992,8 +1620,6 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:noAutofit/>
@@ -1013,7 +1639,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1038,7 +1664,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1063,7 +1689,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1088,7 +1714,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1113,7 +1739,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1138,7 +1764,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1163,7 +1789,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1188,7 +1814,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1213,7 +1839,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1238,7 +1864,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1251,9 +1877,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1264,8 +1896,6 @@
           <a:noFill/>
           <a:miter lim="400000"/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
@@ -1285,19 +1915,19 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Arial"/>
-            <a:ea typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-            <a:sym typeface="Arial"/>
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Arial" panose="020B0604020202090204"/>
+            <a:ea typeface="Arial" panose="020B0604020202090204"/>
+            <a:cs typeface="Arial" panose="020B0604020202090204"/>
+            <a:sym typeface="Arial" panose="020B0604020202090204"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1314,7 +1944,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1339,7 +1969,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1364,7 +1994,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1389,7 +2019,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1414,7 +2044,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1439,7 +2069,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1464,7 +2094,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1489,7 +2119,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1514,7 +2144,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1527,9 +2157,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
@@ -1538,375 +2174,381 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="31.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="76" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3516" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1719" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3482142857143" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1696428571429" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3516" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3482142857143" style="1" customWidth="1"/>
     <col min="7" max="16384" width="12.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" customHeight="1" spans="1:6">
       <c r="A1" s="2"/>
-      <c r="B1" t="s" s="3">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" t="s" s="7">
+      <c r="E1" s="20"/>
+      <c r="F1" s="14"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:6">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s" s="8">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" ht="13.65" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="12"/>
-      <c r="B4" t="s" s="13">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="3" ht="13.65" customHeight="1" spans="1:6">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:6">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" t="s" s="7">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="14"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:6">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s" s="8">
+      <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" t="s" s="7">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:6">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s" s="15">
+      <c r="B6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" t="s" s="7">
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s" s="16">
+      <c r="B7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" t="s" s="16">
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:6">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:6">
+      <c r="A9" s="16"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" t="s" s="7">
+      <c r="B10" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s" s="19">
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" t="s" s="7">
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:6">
+      <c r="A13" s="16"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:6">
+      <c r="A14" s="16"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B11" t="s" s="19">
-        <v>13</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" t="s" s="7">
+      <c r="B16" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:6">
+      <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B12" t="s" s="19">
-        <v>14</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="17"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" t="s" s="7">
-        <v>15</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" t="s" s="7">
-        <v>6</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" t="s" s="7">
-        <v>8</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="17"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" ht="13.65" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="12"/>
-      <c r="B20" t="s" s="13">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s" s="13">
+      <c r="B17" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D20" t="s" s="13">
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:6">
+      <c r="A18" s="16"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+    </row>
+    <row r="19" ht="13.65" customHeight="1" spans="1:6">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:6">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E20" t="s" s="13">
+      <c r="C20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F20" t="s" s="20">
+      <c r="D20" s="11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" t="s" s="7">
+      <c r="E20" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B21" t="s" s="8">
+      <c r="F20" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s" s="21">
+    </row>
+    <row r="21" customHeight="1" spans="1:6">
+      <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="22">
+      <c r="B21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="23">
         <v>1009305716</v>
       </c>
-      <c r="E21" t="s" s="21">
-        <v>24</v>
-      </c>
-      <c r="F21" t="s" s="23">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" t="s" s="7">
+      <c r="E21" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B22" t="s" s="19">
+      <c r="F21" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C22" t="s" s="24">
+    </row>
+    <row r="22" customHeight="1" spans="1:6">
+      <c r="A22" s="5" t="s">
         <v>28</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>30</v>
       </c>
       <c r="D22" s="25">
         <v>1008795074</v>
       </c>
-      <c r="E22" t="s" s="24">
-        <v>29</v>
-      </c>
-      <c r="F22" t="s" s="26">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" t="s" s="7">
+      <c r="E22" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s" s="19">
+      <c r="F22" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C23" t="s" s="24">
+    </row>
+    <row r="23" customHeight="1" spans="1:6">
+      <c r="A23" s="5" t="s">
         <v>33</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>35</v>
       </c>
       <c r="D23" s="25">
         <v>1007241307</v>
       </c>
-      <c r="E23" t="s" s="24">
-        <v>34</v>
-      </c>
-      <c r="F23" t="s" s="24">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" t="s" s="7">
+      <c r="E23" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B24" t="s" s="19">
+      <c r="F23" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C24" t="s" s="24">
+    </row>
+    <row r="24" customHeight="1" spans="1:6">
+      <c r="A24" s="5" t="s">
         <v>38</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>40</v>
       </c>
       <c r="D24" s="25">
         <v>1010770444</v>
       </c>
-      <c r="E24" t="s" s="24">
-        <v>39</v>
-      </c>
-      <c r="F24" t="s" s="24">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" t="s" s="7">
+      <c r="E24" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" ht="13.65" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" t="s" s="24">
+      <c r="F24" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" t="s" s="24">
+    </row>
+    <row r="25" customHeight="1" spans="1:6">
+      <c r="A25" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" t="s" s="24">
+      <c r="B25" s="20"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" ht="13.65" customHeight="1" spans="1:6">
+      <c r="A26" s="7"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:6">
+      <c r="A27" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" t="s" s="24">
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:6">
+      <c r="A28" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:6">
+      <c r="A29" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:6">
+      <c r="A30" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F21" r:id="rId1" location="" tooltip="" display="https://github.com/CSJ111"/>
-    <hyperlink ref="F22" r:id="rId2" location="" tooltip="" display="https://github.com/q1ngyao"/>
-    <hyperlink ref="F24" r:id="rId3" location="" tooltip="" display="https://github.com/char1029"/>
+    <hyperlink ref="F21" r:id="rId1" display="https://github.com/CSJ111"/>
+    <hyperlink ref="F22" r:id="rId2" display="https://github.com/q1ngyao"/>
+    <hyperlink ref="F24" r:id="rId3" display="https://github.com/char1029"/>
+    <hyperlink ref="F23" r:id="rId4" display="https://github.com/DMZ66"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21960" windowHeight="12680"/>
+    <workbookView windowWidth="21960" windowHeight="12660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,10 +65,10 @@
     <t>Acceptance-Rejection Method(Topic 2)</t>
   </si>
   <si>
-    <t>Acceptance-Rejection for Laplace Distribution</t>
-  </si>
-  <si>
-    <t>We use the acceptance–rejection method to generate random samples from the Laplace distribution and assess the accuracy of the simulated results by comparing the empirical density, mean, and variance with their theoretical counterparts.</t>
+    <t>Acceptance-Rejection for Laplace Distribution and Log-logistic distribution</t>
+  </si>
+  <si>
+    <t>We use the acceptance–rejection method to generate random samples from the Laplace distribution &amp; Log-Logistic distribution and assess the accuracy of the simulated results by comparing the empirical density, mean, and variance with their theoretical counterparts.</t>
   </si>
   <si>
     <t>Topic Number 3</t>

--- a/STA380GroupForm.xlsx
+++ b/STA380GroupForm.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\STA380\STA380project\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083E6859-A37D-4B1C-A7AC-C3882B2FD0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21960" windowHeight="12660"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,12 +28,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -116,7 +125,7 @@
         <sz val="10"/>
         <color indexed="12"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://github.com/CSJ111</t>
     </r>
@@ -140,7 +149,7 @@
         <sz val="10"/>
         <color indexed="12"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://github.com/q1ngyao</t>
     </r>
@@ -179,7 +188,7 @@
         <sz val="10"/>
         <color indexed="12"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>https://github.com/char1029</t>
     </r>
@@ -198,19 +207,24 @@
   </si>
   <si>
     <t>To report an inactive member, please refer to the "Reporting Inactive Members" section under the project description.</t>
+  </si>
+  <si>
+    <t>Yanming Zhao</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>zhaoy439</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/Yanming41</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -223,181 +237,49 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,194 +298,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="19">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -725,253 +421,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1007,59 +464,15 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
@@ -1132,6 +545,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1338,7 +754,7 @@
           <a:miter lim="800000"/>
         </a:ln>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1621,7 +1037,7 @@
           <a:miter lim="800000"/>
         </a:ln>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1897,7 +1313,7 @@
           <a:miter lim="400000"/>
         </a:ln>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2170,25 +1586,26 @@
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="12.46875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.46875" style="1" customWidth="1"/>
     <col min="2" max="2" width="76" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3482142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1696428571429" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.3482142857143" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="12.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.17578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.46875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.46875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="12.46875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:6">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -2198,7 +1615,7 @@
       <c r="E1" s="20"/>
       <c r="F1" s="14"/>
     </row>
-    <row r="2" customHeight="1" spans="1:6">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -2210,7 +1627,7 @@
       <c r="E2" s="14"/>
       <c r="F2" s="14"/>
     </row>
-    <row r="3" ht="13.65" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" ht="13.7" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -2218,7 +1635,7 @@
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
     </row>
-    <row r="4" customHeight="1" spans="1:6">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="11" t="s">
         <v>3</v>
@@ -2228,7 +1645,7 @@
       <c r="E4" s="20"/>
       <c r="F4" s="14"/>
     </row>
-    <row r="5" customHeight="1" spans="1:6">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -2240,7 +1657,7 @@
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
     </row>
-    <row r="6" customHeight="1" spans="1:6">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -2252,7 +1669,7 @@
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" customHeight="1" spans="1:6">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -2264,7 +1681,7 @@
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
     </row>
-    <row r="8" customHeight="1" spans="1:6">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="16"/>
       <c r="B8" s="17"/>
       <c r="C8" s="14"/>
@@ -2272,7 +1689,7 @@
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" customHeight="1" spans="1:6">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="18"/>
       <c r="C9" s="14"/>
@@ -2280,7 +1697,7 @@
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
     </row>
-    <row r="10" customHeight="1" spans="1:6">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -2292,7 +1709,7 @@
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
     </row>
-    <row r="11" customHeight="1" spans="1:6">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -2304,7 +1721,7 @@
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" customHeight="1" spans="1:6">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
@@ -2316,7 +1733,7 @@
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
     </row>
-    <row r="13" customHeight="1" spans="1:6">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="16"/>
       <c r="B13" s="20"/>
       <c r="C13" s="14"/>
@@ -2324,7 +1741,7 @@
       <c r="E13" s="14"/>
       <c r="F13" s="14"/>
     </row>
-    <row r="14" customHeight="1" spans="1:6">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="16"/>
       <c r="B14" s="20"/>
       <c r="C14" s="14"/>
@@ -2332,7 +1749,7 @@
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
     </row>
-    <row r="15" customHeight="1" spans="1:6">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
@@ -2344,7 +1761,7 @@
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
     </row>
-    <row r="16" customHeight="1" spans="1:6">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>6</v>
       </c>
@@ -2356,7 +1773,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="14"/>
     </row>
-    <row r="17" customHeight="1" spans="1:6">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -2368,7 +1785,7 @@
       <c r="E17" s="14"/>
       <c r="F17" s="14"/>
     </row>
-    <row r="18" customHeight="1" spans="1:6">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="16"/>
       <c r="B18" s="20"/>
       <c r="C18" s="14"/>
@@ -2376,7 +1793,7 @@
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
     </row>
-    <row r="19" ht="13.65" customHeight="1" spans="1:6">
+    <row r="19" spans="1:6" ht="13.7" customHeight="1">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -2384,7 +1801,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" customHeight="1" spans="1:6">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="11" t="s">
         <v>18</v>
@@ -2402,7 +1819,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:6">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
@@ -2422,7 +1839,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:6">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>28</v>
       </c>
@@ -2442,7 +1859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:6">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>33</v>
       </c>
@@ -2462,7 +1879,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:6">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
@@ -2482,17 +1899,27 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:6">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-    </row>
-    <row r="26" ht="13.65" customHeight="1" spans="1:6">
+      <c r="B25" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="14">
+        <v>1010452895</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="13.7" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -2500,7 +1927,7 @@
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
     </row>
-    <row r="27" customHeight="1" spans="1:6">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="24" t="s">
         <v>44</v>
       </c>
@@ -2510,7 +1937,7 @@
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
     </row>
-    <row r="28" customHeight="1" spans="1:6">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="24" t="s">
         <v>45</v>
       </c>
@@ -2520,7 +1947,7 @@
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
     </row>
-    <row r="29" customHeight="1" spans="1:6">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="24" t="s">
         <v>46</v>
       </c>
@@ -2530,7 +1957,7 @@
       <c r="E29" s="14"/>
       <c r="F29" s="14"/>
     </row>
-    <row r="30" customHeight="1" spans="1:6">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="24" t="s">
         <v>47</v>
       </c>
@@ -2541,14 +1968,15 @@
       <c r="F30" s="14"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F21" r:id="rId1" display="https://github.com/CSJ111"/>
-    <hyperlink ref="F22" r:id="rId2" display="https://github.com/q1ngyao"/>
-    <hyperlink ref="F24" r:id="rId3" display="https://github.com/char1029"/>
-    <hyperlink ref="F23" r:id="rId4" display="https://github.com/DMZ66"/>
+    <hyperlink ref="F21" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F22" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F24" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F23" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
